--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_valparaiso.xlsx
@@ -147,7 +147,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:24</t>
+    <t xml:space="preserve">2026-09-09 20:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_valparaiso.xlsx
@@ -24,120 +24,120 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Fernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Pascua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Algarrobo</t>
   </si>
   <si>
-    <t xml:space="preserve">Cabildo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Larga</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
-    <t xml:space="preserve">Casablanca</t>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Tabo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
     <t xml:space="preserve">Catemu</t>
   </si>
   <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Quisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Tabo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hijuelas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Pascua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Fernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
   </si>
   <si>
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
-    <t xml:space="preserve">Llaillay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Olmué</t>
   </si>
   <si>
-    <t xml:space="preserve">Panquehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puchuncaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilpué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinconada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Felipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
-    <t xml:space="preserve">Viña del Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zapallar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -147,7 +147,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:22</t>
+    <t xml:space="preserve">2026-09-18 10:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -559,7 +559,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>70.2</v>
+        <v>71.9</v>
       </c>
     </row>
     <row r="3">
@@ -567,7 +567,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>71.92</v>
+        <v>73.93</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>74.74</v>
+        <v>74.39</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>72.52</v>
+        <v>78.82</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>72.67</v>
+        <v>75.32</v>
       </c>
     </row>
     <row r="7">
@@ -599,7 +599,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>73.93</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>73.13</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>74.39</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="10">
@@ -623,7 +623,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>68.51</v>
+        <v>72.59</v>
       </c>
     </row>
     <row r="11">
@@ -631,7 +631,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>71.23</v>
+        <v>72.52</v>
       </c>
     </row>
     <row r="12">
@@ -639,7 +639,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>73.24</v>
+        <v>74.88</v>
       </c>
     </row>
     <row r="13">
@@ -647,7 +647,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>67.2</v>
+        <v>73.31</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>78.82</v>
+        <v>72.42</v>
       </c>
     </row>
     <row r="15">
@@ -663,7 +663,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>76.68</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="16">
@@ -671,7 +671,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>72.42</v>
+        <v>72.01</v>
       </c>
     </row>
     <row r="17">
@@ -679,7 +679,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>72.07</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="18">
@@ -687,7 +687,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>74.74</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="19">
@@ -695,7 +695,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>72.59</v>
+        <v>74.79</v>
       </c>
     </row>
     <row r="20">
@@ -703,7 +703,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>73.47</v>
+        <v>74.74</v>
       </c>
     </row>
     <row r="21">
@@ -711,7 +711,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>70.22</v>
+        <v>73.24</v>
       </c>
     </row>
     <row r="22">
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>72.6</v>
+        <v>76.68</v>
       </c>
     </row>
     <row r="23">
@@ -727,7 +727,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>72.01</v>
+        <v>73.47</v>
       </c>
     </row>
     <row r="24">
@@ -735,7 +735,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>72.06</v>
+        <v>72.52</v>
       </c>
     </row>
     <row r="25">
@@ -743,7 +743,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>75.32</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="26">
@@ -751,7 +751,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>74.18</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="27">
@@ -759,7 +759,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>74.79</v>
+        <v>68.51</v>
       </c>
     </row>
     <row r="28">
@@ -767,7 +767,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>75.3</v>
+        <v>71.23</v>
       </c>
     </row>
     <row r="29">
@@ -775,7 +775,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>72.06</v>
+        <v>75.72</v>
       </c>
     </row>
     <row r="30">
@@ -783,7 +783,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>74.88</v>
+        <v>72.91</v>
       </c>
     </row>
     <row r="31">
@@ -791,7 +791,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>72.52</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="32">
@@ -799,7 +799,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>73.31</v>
+        <v>74.74</v>
       </c>
     </row>
     <row r="33">
@@ -807,7 +807,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>72.91</v>
+        <v>72.6</v>
       </c>
     </row>
     <row r="34">
@@ -815,7 +815,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>74.12</v>
+        <v>74.18</v>
       </c>
     </row>
     <row r="35">
@@ -823,7 +823,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>75.72</v>
+        <v>74.12</v>
       </c>
     </row>
     <row r="36">
@@ -831,7 +831,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>71.9</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="37">
@@ -839,7 +839,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>75.2</v>
+        <v>72.07</v>
       </c>
     </row>
     <row r="38">
@@ -847,7 +847,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>73.62</v>
+        <v>70.22</v>
       </c>
     </row>
     <row r="39">
@@ -855,7 +855,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>70.41</v>
+        <v>75.2</v>
       </c>
     </row>
   </sheetData>
